--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -13033,13 +13033,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13344,13 +13346,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q656"/>
+  <dimension ref="A1:V656"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13403,7 +13409,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -13449,8 +13455,11 @@
       <c r="O2" t="s">
         <v>1269</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q2">
+        <v>9100001135187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -13470,7 +13479,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -13490,7 +13499,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>632</v>
       </c>
@@ -13510,7 +13519,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -13530,7 +13539,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -13579,8 +13588,10 @@
       <c r="Q7">
         <v>21167045</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T7" s="4"/>
+      <c r="V7" s="5"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -13630,7 +13641,7 @@
         <v>21171287</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -13680,7 +13691,7 @@
         <v>21167169</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -13730,7 +13741,7 @@
         <v>21216852</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -13780,7 +13791,7 @@
         <v>21199966</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -13830,7 +13841,7 @@
         <v>21154032</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -13880,7 +13891,7 @@
         <v>21195685</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -13930,7 +13941,7 @@
         <v>21175277</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -13974,7 +13985,7 @@
         <v>21181161</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>29</v>
       </c>

--- a/data/employees.xlsx
+++ b/data/employees.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13461" uniqueCount="5426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14181" uniqueCount="5427">
   <si>
     <t>Employee ID</t>
   </si>
@@ -16297,6 +16297,9 @@
   </si>
   <si>
     <t>Mwabulawo</t>
+  </si>
+  <si>
+    <t>B1</t>
   </si>
 </sst>
 </file>
@@ -16304,7 +16307,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -16360,7 +16363,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -16668,6 +16671,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -61085,7 +61089,7 @@
         <v>25</v>
       </c>
       <c r="I993" t="s">
-        <v>4342</v>
+        <v>5426</v>
       </c>
       <c r="J993" t="s">
         <v>1208</v>
@@ -61122,6 +61126,15 @@
       <c r="E994" t="s">
         <v>5048</v>
       </c>
+      <c r="H994" t="s">
+        <v>50</v>
+      </c>
+      <c r="I994" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q994" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="995" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
@@ -61139,6 +61152,15 @@
       <c r="E995" t="s">
         <v>5048</v>
       </c>
+      <c r="H995" t="s">
+        <v>50</v>
+      </c>
+      <c r="I995" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q995" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="996" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
@@ -61156,6 +61178,15 @@
       <c r="E996" t="s">
         <v>5048</v>
       </c>
+      <c r="H996" t="s">
+        <v>50</v>
+      </c>
+      <c r="I996" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q996" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="997" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
@@ -61173,6 +61204,15 @@
       <c r="E997" t="s">
         <v>5048</v>
       </c>
+      <c r="H997" t="s">
+        <v>50</v>
+      </c>
+      <c r="I997" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q997" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="998" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
@@ -61190,6 +61230,15 @@
       <c r="E998" t="s">
         <v>5048</v>
       </c>
+      <c r="H998" t="s">
+        <v>50</v>
+      </c>
+      <c r="I998" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q998" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="999" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
@@ -61207,6 +61256,15 @@
       <c r="E999" t="s">
         <v>5048</v>
       </c>
+      <c r="H999" t="s">
+        <v>50</v>
+      </c>
+      <c r="I999" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q999" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1000" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
@@ -61224,6 +61282,15 @@
       <c r="E1000" t="s">
         <v>5048</v>
       </c>
+      <c r="H1000" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1000" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1000" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1001" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
@@ -61241,6 +61308,15 @@
       <c r="E1001" t="s">
         <v>5048</v>
       </c>
+      <c r="H1001" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1001" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1001" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1002" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
@@ -61258,6 +61334,15 @@
       <c r="E1002" t="s">
         <v>5048</v>
       </c>
+      <c r="H1002" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1002" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1002" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1003" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
@@ -61275,6 +61360,15 @@
       <c r="E1003" t="s">
         <v>5048</v>
       </c>
+      <c r="H1003" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1003" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1003" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1004" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
@@ -61292,6 +61386,15 @@
       <c r="E1004" t="s">
         <v>5048</v>
       </c>
+      <c r="H1004" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1004" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1004" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1005" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
@@ -61309,6 +61412,15 @@
       <c r="E1005" t="s">
         <v>5048</v>
       </c>
+      <c r="H1005" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1005" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1005" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1006" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
@@ -61326,6 +61438,15 @@
       <c r="E1006" t="s">
         <v>5048</v>
       </c>
+      <c r="H1006" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1006" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1006" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1007" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
@@ -61343,6 +61464,15 @@
       <c r="E1007" t="s">
         <v>5048</v>
       </c>
+      <c r="H1007" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1007" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1007" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="1008" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
@@ -61360,8 +61490,17 @@
       <c r="E1008" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1009" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1008" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1008" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1008" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>5076</v>
       </c>
@@ -61377,8 +61516,17 @@
       <c r="E1009" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1010" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1009" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1009" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1009" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>5078</v>
       </c>
@@ -61394,8 +61542,17 @@
       <c r="E1010" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1011" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1010" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1010" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1010" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>5080</v>
       </c>
@@ -61411,8 +61568,17 @@
       <c r="E1011" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1012" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1011" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1011" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1011" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>5082</v>
       </c>
@@ -61428,8 +61594,17 @@
       <c r="E1012" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1013" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1012" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1012" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1012" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>5084</v>
       </c>
@@ -61445,8 +61620,17 @@
       <c r="E1013" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1014" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1013" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1013" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1013" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>5086</v>
       </c>
@@ -61462,8 +61646,17 @@
       <c r="E1014" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1015" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1014" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1014" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1014" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>5088</v>
       </c>
@@ -61479,8 +61672,17 @@
       <c r="E1015" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1016" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1015" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1015" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1015" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>5090</v>
       </c>
@@ -61496,8 +61698,17 @@
       <c r="E1016" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1017" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1016" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1016" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1016" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>5092</v>
       </c>
@@ -61513,8 +61724,17 @@
       <c r="E1017" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1018" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1017" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1017" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1017" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>5094</v>
       </c>
@@ -61530,8 +61750,17 @@
       <c r="E1018" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1019" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1018" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1018" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1018" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>5096</v>
       </c>
@@ -61547,8 +61776,17 @@
       <c r="E1019" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1020" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1019" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1019" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>5098</v>
       </c>
@@ -61564,8 +61802,17 @@
       <c r="E1020" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1021" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1020" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1020" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1020" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>5100</v>
       </c>
@@ -61581,8 +61828,17 @@
       <c r="E1021" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1022" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1021" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1021" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>5102</v>
       </c>
@@ -61598,8 +61854,17 @@
       <c r="E1022" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1023" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1022" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1022" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1022" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>5103</v>
       </c>
@@ -61615,8 +61880,17 @@
       <c r="E1023" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1024" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1023" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1023" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1023" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>5104</v>
       </c>
@@ -61632,8 +61906,17 @@
       <c r="E1024" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1025" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1024" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1024" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1024" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>5105</v>
       </c>
@@ -61649,8 +61932,17 @@
       <c r="E1025" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1026" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1025" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1025" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1025" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>5106</v>
       </c>
@@ -61666,8 +61958,17 @@
       <c r="E1026" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1027" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1026" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1026" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1026" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>5107</v>
       </c>
@@ -61683,8 +61984,17 @@
       <c r="E1027" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1028" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1027" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1027" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1027" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>5108</v>
       </c>
@@ -61700,8 +62010,17 @@
       <c r="E1028" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1029" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1028" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1028" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1028" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>5109</v>
       </c>
@@ -61717,8 +62036,17 @@
       <c r="E1029" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1030" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1029" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1029" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1029" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>5110</v>
       </c>
@@ -61734,8 +62062,17 @@
       <c r="E1030" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1031" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1030" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1030" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>5111</v>
       </c>
@@ -61751,8 +62088,17 @@
       <c r="E1031" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1032" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1031" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1031" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1031" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>5112</v>
       </c>
@@ -61768,8 +62114,17 @@
       <c r="E1032" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1033" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1032" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1032" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>5113</v>
       </c>
@@ -61785,8 +62140,17 @@
       <c r="E1033" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1034" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1033" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1033" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1033" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>5114</v>
       </c>
@@ -61802,8 +62166,17 @@
       <c r="E1034" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1035" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1034" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1034" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1034" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>5116</v>
       </c>
@@ -61819,8 +62192,17 @@
       <c r="E1035" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1036" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1035" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1035" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1035" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>5117</v>
       </c>
@@ -61836,8 +62218,17 @@
       <c r="E1036" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1037" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1036" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1036" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1036" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>5118</v>
       </c>
@@ -61853,8 +62244,17 @@
       <c r="E1037" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1038" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1037" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1037" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1037" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>5119</v>
       </c>
@@ -61870,8 +62270,17 @@
       <c r="E1038" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1039" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1038" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1038" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1038" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>5120</v>
       </c>
@@ -61887,8 +62296,17 @@
       <c r="E1039" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1040" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1039" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1039" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1039" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>5121</v>
       </c>
@@ -61904,8 +62322,17 @@
       <c r="E1040" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1041" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1040" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1040" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1040" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>5122</v>
       </c>
@@ -61921,8 +62348,17 @@
       <c r="E1041" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1042" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1041" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1041" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1041" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>5123</v>
       </c>
@@ -61938,8 +62374,17 @@
       <c r="E1042" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1043" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1042" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1042" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1042" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>5124</v>
       </c>
@@ -61955,8 +62400,17 @@
       <c r="E1043" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1044" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1043" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1043" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1043" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>5125</v>
       </c>
@@ -61972,8 +62426,17 @@
       <c r="E1044" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1045" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1044" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1044" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1044" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>5126</v>
       </c>
@@ -61989,8 +62452,17 @@
       <c r="E1045" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1046" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1045" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1045" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1045" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>5127</v>
       </c>
@@ -62006,8 +62478,17 @@
       <c r="E1046" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1047" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1046" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1046" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>5128</v>
       </c>
@@ -62023,8 +62504,17 @@
       <c r="E1047" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1048" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1047" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1047" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1047" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>5129</v>
       </c>
@@ -62040,8 +62530,17 @@
       <c r="E1048" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1049" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1048" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1048" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1048" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>5130</v>
       </c>
@@ -62057,8 +62556,17 @@
       <c r="E1049" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1050" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1049" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1049" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1049" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>5131</v>
       </c>
@@ -62074,8 +62582,17 @@
       <c r="E1050" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1051" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1050" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1050" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1050" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>5132</v>
       </c>
@@ -62091,8 +62608,17 @@
       <c r="E1051" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1052" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1051" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1051" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1051" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
         <v>5133</v>
       </c>
@@ -62108,8 +62634,17 @@
       <c r="E1052" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1053" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1052" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1052" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1052" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
         <v>5134</v>
       </c>
@@ -62125,8 +62660,17 @@
       <c r="E1053" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1054" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1053" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1053" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1053" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
         <v>5135</v>
       </c>
@@ -62142,8 +62686,17 @@
       <c r="E1054" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1055" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1054" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1054" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1054" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
         <v>5136</v>
       </c>
@@ -62159,8 +62712,17 @@
       <c r="E1055" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1056" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1055" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1055" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1055" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
         <v>5137</v>
       </c>
@@ -62176,8 +62738,17 @@
       <c r="E1056" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1057" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1056" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1056" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1056" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
         <v>5138</v>
       </c>
@@ -62193,8 +62764,17 @@
       <c r="E1057" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1058" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1057" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1057" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1057" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
         <v>5139</v>
       </c>
@@ -62210,8 +62790,17 @@
       <c r="E1058" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1059" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1058" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1058" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1058" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
         <v>5140</v>
       </c>
@@ -62227,8 +62816,17 @@
       <c r="E1059" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1060" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1059" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1059" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1059" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
         <v>5141</v>
       </c>
@@ -62244,8 +62842,17 @@
       <c r="E1060" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1061" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1060" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1060" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1060" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
         <v>5142</v>
       </c>
@@ -62261,8 +62868,17 @@
       <c r="E1061" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1062" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1061" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1061" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1061" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
         <v>5143</v>
       </c>
@@ -62278,8 +62894,17 @@
       <c r="E1062" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1063" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1062" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1062" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1062" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
         <v>5144</v>
       </c>
@@ -62295,8 +62920,17 @@
       <c r="E1063" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1064" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1063" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1063" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1063" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
         <v>5145</v>
       </c>
@@ -62312,8 +62946,17 @@
       <c r="E1064" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1065" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1064" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1064" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
         <v>5146</v>
       </c>
@@ -62329,8 +62972,17 @@
       <c r="E1065" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1066" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1065" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1065" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
         <v>5147</v>
       </c>
@@ -62346,8 +62998,17 @@
       <c r="E1066" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1067" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1066" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1066" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
         <v>5148</v>
       </c>
@@ -62363,8 +63024,17 @@
       <c r="E1067" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1068" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1067" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1067" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
         <v>5149</v>
       </c>
@@ -62380,8 +63050,17 @@
       <c r="E1068" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1069" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1068" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1068" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
         <v>5150</v>
       </c>
@@ -62397,8 +63076,17 @@
       <c r="E1069" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1070" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1069" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1069" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1069" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
         <v>5151</v>
       </c>
@@ -62414,8 +63102,17 @@
       <c r="E1070" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1070" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1070" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
         <v>5152</v>
       </c>
@@ -62431,8 +63128,17 @@
       <c r="E1071" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1071" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1071" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1072" t="s">
         <v>5153</v>
       </c>
@@ -62448,8 +63154,17 @@
       <c r="E1072" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1072" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1072" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1073" t="s">
         <v>5154</v>
       </c>
@@ -62465,8 +63180,17 @@
       <c r="E1073" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1074" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1073" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1073" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1074" t="s">
         <v>5156</v>
       </c>
@@ -62482,8 +63206,17 @@
       <c r="E1074" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1075" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1074" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1074" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1074" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1075" t="s">
         <v>5157</v>
       </c>
@@ -62499,8 +63232,17 @@
       <c r="E1075" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1076" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1075" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1075" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1075" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1076" t="s">
         <v>5158</v>
       </c>
@@ -62516,8 +63258,17 @@
       <c r="E1076" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1077" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1076" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1076" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1076" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1077" t="s">
         <v>5159</v>
       </c>
@@ -62533,8 +63284,17 @@
       <c r="E1077" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1077" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1077" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1077" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1078" t="s">
         <v>5160</v>
       </c>
@@ -62550,8 +63310,17 @@
       <c r="E1078" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1079" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1078" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1078" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1078" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1079" t="s">
         <v>5162</v>
       </c>
@@ -62567,8 +63336,17 @@
       <c r="E1079" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1079" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1079" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1079" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
         <v>5163</v>
       </c>
@@ -62584,8 +63362,17 @@
       <c r="E1080" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1080" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1080" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1080" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
         <v>5164</v>
       </c>
@@ -62601,8 +63388,17 @@
       <c r="E1081" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1081" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1081" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1081" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
         <v>5165</v>
       </c>
@@ -62618,8 +63414,17 @@
       <c r="E1082" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1082" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1082" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1082" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
         <v>5166</v>
       </c>
@@ -62635,8 +63440,17 @@
       <c r="E1083" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1083" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1083" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1083" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
         <v>5167</v>
       </c>
@@ -62652,8 +63466,17 @@
       <c r="E1084" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1084" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1084" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1084" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
         <v>5168</v>
       </c>
@@ -62669,8 +63492,17 @@
       <c r="E1085" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1085" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1085" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1085" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
         <v>5169</v>
       </c>
@@ -62686,8 +63518,17 @@
       <c r="E1086" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1086" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1086" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1086" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1087" t="s">
         <v>5171</v>
       </c>
@@ -62703,8 +63544,17 @@
       <c r="E1087" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1087" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1087" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1087" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
         <v>5172</v>
       </c>
@@ -62720,8 +63570,17 @@
       <c r="E1088" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1088" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1088" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1088" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
         <v>5173</v>
       </c>
@@ -62737,8 +63596,17 @@
       <c r="E1089" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1089" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1089" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1089" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
         <v>5174</v>
       </c>
@@ -62754,8 +63622,17 @@
       <c r="E1090" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1090" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1090" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1090" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
         <v>5176</v>
       </c>
@@ -62771,8 +63648,17 @@
       <c r="E1091" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1091" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1091" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1091" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1092" t="s">
         <v>5177</v>
       </c>
@@ -62788,8 +63674,17 @@
       <c r="E1092" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1092" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1092" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1092" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1093" t="s">
         <v>5178</v>
       </c>
@@ -62805,8 +63700,17 @@
       <c r="E1093" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1093" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1093" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1093" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1094" t="s">
         <v>5180</v>
       </c>
@@ -62822,8 +63726,17 @@
       <c r="E1094" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1094" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1094" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1094" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
         <v>5181</v>
       </c>
@@ -62839,8 +63752,17 @@
       <c r="E1095" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1095" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1095" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1095" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
         <v>5182</v>
       </c>
@@ -62856,8 +63778,17 @@
       <c r="E1096" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1096" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1096" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1096" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
         <v>5183</v>
       </c>
@@ -62873,8 +63804,17 @@
       <c r="E1097" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1097" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1097" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1097" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
         <v>5185</v>
       </c>
@@ -62890,8 +63830,17 @@
       <c r="E1098" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1098" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1098" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1098" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
         <v>5187</v>
       </c>
@@ -62907,8 +63856,17 @@
       <c r="E1099" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1099" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1099" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1099" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
         <v>5189</v>
       </c>
@@ -62924,8 +63882,17 @@
       <c r="E1100" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1100" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1100" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1100" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
         <v>5191</v>
       </c>
@@ -62941,8 +63908,17 @@
       <c r="E1101" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1101" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1101" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
         <v>5193</v>
       </c>
@@ -62958,8 +63934,17 @@
       <c r="E1102" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1102" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1102" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
         <v>5194</v>
       </c>
@@ -62975,8 +63960,17 @@
       <c r="E1103" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1103" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1103" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
         <v>5195</v>
       </c>
@@ -62992,8 +63986,17 @@
       <c r="E1104" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1104" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1104" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
         <v>5197</v>
       </c>
@@ -63009,8 +64012,17 @@
       <c r="E1105" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1105" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1105" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
         <v>5199</v>
       </c>
@@ -63026,8 +64038,17 @@
       <c r="E1106" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1106" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1106" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1106" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
         <v>5201</v>
       </c>
@@ -63043,8 +64064,17 @@
       <c r="E1107" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1107" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1107" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1107" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
         <v>5202</v>
       </c>
@@ -63060,8 +64090,17 @@
       <c r="E1108" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1108" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1108" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
         <v>5203</v>
       </c>
@@ -63077,8 +64116,17 @@
       <c r="E1109" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1109" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1109" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
         <v>5205</v>
       </c>
@@ -63094,8 +64142,17 @@
       <c r="E1110" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1110" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1110" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1110" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
         <v>5207</v>
       </c>
@@ -63111,8 +64168,17 @@
       <c r="E1111" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1111" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1111" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1111" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
         <v>5208</v>
       </c>
@@ -63128,8 +64194,17 @@
       <c r="E1112" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1112" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1112" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1112" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
         <v>5210</v>
       </c>
@@ -63145,8 +64220,17 @@
       <c r="E1113" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1113" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1113" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1113" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
         <v>5212</v>
       </c>
@@ -63162,8 +64246,17 @@
       <c r="E1114" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1114" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1114" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1114" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
         <v>5214</v>
       </c>
@@ -63179,8 +64272,17 @@
       <c r="E1115" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1115" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1115" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1115" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
         <v>5215</v>
       </c>
@@ -63196,8 +64298,17 @@
       <c r="E1116" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1116" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1116" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1116" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
         <v>5217</v>
       </c>
@@ -63213,8 +64324,17 @@
       <c r="E1117" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1117" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1117" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1117" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
         <v>5218</v>
       </c>
@@ -63230,8 +64350,17 @@
       <c r="E1118" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1118" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1118" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1118" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
         <v>5220</v>
       </c>
@@ -63247,8 +64376,17 @@
       <c r="E1119" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1119" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1119" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1119" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
         <v>5222</v>
       </c>
@@ -63264,8 +64402,17 @@
       <c r="E1120" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1120" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1120" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
         <v>5224</v>
       </c>
@@ -63281,8 +64428,17 @@
       <c r="E1121" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1121" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1121" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1121" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
         <v>5225</v>
       </c>
@@ -63298,8 +64454,17 @@
       <c r="E1122" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1122" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1122" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1122" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
         <v>5226</v>
       </c>
@@ -63315,8 +64480,17 @@
       <c r="E1123" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1123" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1123" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1123" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
         <v>5228</v>
       </c>
@@ -63332,8 +64506,17 @@
       <c r="E1124" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1124" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1124" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1124" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
         <v>5230</v>
       </c>
@@ -63349,8 +64532,17 @@
       <c r="E1125" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1125" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1125" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1125" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
         <v>5232</v>
       </c>
@@ -63366,8 +64558,17 @@
       <c r="E1126" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1126" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1126" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1126" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
         <v>5234</v>
       </c>
@@ -63383,8 +64584,17 @@
       <c r="E1127" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1127" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1127" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1127" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
         <v>5236</v>
       </c>
@@ -63400,8 +64610,17 @@
       <c r="E1128" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1128" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1128" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1128" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
         <v>5238</v>
       </c>
@@ -63417,8 +64636,17 @@
       <c r="E1129" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1129" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1129" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1129" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
         <v>5240</v>
       </c>
@@ -63434,8 +64662,17 @@
       <c r="E1130" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1130" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1130" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1130" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
         <v>5242</v>
       </c>
@@ -63451,8 +64688,17 @@
       <c r="E1131" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1131" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1131" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1131" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
         <v>5244</v>
       </c>
@@ -63468,8 +64714,17 @@
       <c r="E1132" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1132" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1132" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1132" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
         <v>5246</v>
       </c>
@@ -63485,8 +64740,17 @@
       <c r="E1133" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1133" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1133" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1133" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
         <v>5248</v>
       </c>
@@ -63502,8 +64766,17 @@
       <c r="E1134" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1134" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1134" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1134" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
         <v>5250</v>
       </c>
@@ -63519,8 +64792,17 @@
       <c r="E1135" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1135" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1135" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1135" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
         <v>5252</v>
       </c>
@@ -63536,8 +64818,17 @@
       <c r="E1136" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1136" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1136" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1136" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
         <v>5254</v>
       </c>
@@ -63553,8 +64844,17 @@
       <c r="E1137" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1137" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1137" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1137" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
         <v>5256</v>
       </c>
@@ -63570,8 +64870,17 @@
       <c r="E1138" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1138" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1138" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1138" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
         <v>5258</v>
       </c>
@@ -63587,8 +64896,17 @@
       <c r="E1139" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1139" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1139" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1139" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
         <v>5260</v>
       </c>
@@ -63604,8 +64922,17 @@
       <c r="E1140" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1140" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1140" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1140" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
         <v>5262</v>
       </c>
@@ -63621,8 +64948,17 @@
       <c r="E1141" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1141" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1141" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1141" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
         <v>5264</v>
       </c>
@@ -63638,8 +64974,17 @@
       <c r="E1142" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1142" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1142" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1142" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
         <v>5266</v>
       </c>
@@ -63655,8 +65000,17 @@
       <c r="E1143" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1143" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1143" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1143" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
         <v>5268</v>
       </c>
@@ -63672,8 +65026,17 @@
       <c r="E1144" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1144" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1144" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1144" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
         <v>5270</v>
       </c>
@@ -63689,8 +65052,17 @@
       <c r="E1145" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1145" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1145" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1145" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
         <v>5271</v>
       </c>
@@ -63706,8 +65078,17 @@
       <c r="E1146" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1146" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1146" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1146" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
         <v>5273</v>
       </c>
@@ -63723,8 +65104,17 @@
       <c r="E1147" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1147" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1147" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1147" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
         <v>5275</v>
       </c>
@@ -63740,8 +65130,17 @@
       <c r="E1148" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1148" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1148" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1148" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
         <v>5277</v>
       </c>
@@ -63757,8 +65156,17 @@
       <c r="E1149" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1149" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1149" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1149" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
         <v>5279</v>
       </c>
@@ -63774,8 +65182,17 @@
       <c r="E1150" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1150" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1150" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1150" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
         <v>5280</v>
       </c>
@@ -63791,8 +65208,17 @@
       <c r="E1151" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1151" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1151" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1151" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
         <v>5282</v>
       </c>
@@ -63808,8 +65234,17 @@
       <c r="E1152" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1152" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1152" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1152" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
         <v>5284</v>
       </c>
@@ -63825,8 +65260,17 @@
       <c r="E1153" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1153" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1153" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1153" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
         <v>5286</v>
       </c>
@@ -63842,8 +65286,17 @@
       <c r="E1154" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1154" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1154" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1154" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
         <v>5288</v>
       </c>
@@ -63859,8 +65312,17 @@
       <c r="E1155" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1155" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1155" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1155" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
         <v>5290</v>
       </c>
@@ -63876,8 +65338,17 @@
       <c r="E1156" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1156" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1156" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1156" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
         <v>5292</v>
       </c>
@@ -63893,8 +65364,17 @@
       <c r="E1157" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1157" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1157" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1157" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
         <v>5294</v>
       </c>
@@ -63910,8 +65390,17 @@
       <c r="E1158" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1158" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1158" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1158" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
         <v>5296</v>
       </c>
@@ -63927,8 +65416,17 @@
       <c r="E1159" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1159" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1159" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1159" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
         <v>5298</v>
       </c>
@@ -63944,8 +65442,17 @@
       <c r="E1160" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1160" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1160" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1160" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
         <v>5300</v>
       </c>
@@ -63961,8 +65468,17 @@
       <c r="E1161" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1161" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1161" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
         <v>5302</v>
       </c>
@@ -63978,8 +65494,17 @@
       <c r="E1162" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1162" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1162" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1162" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
         <v>5304</v>
       </c>
@@ -63995,8 +65520,17 @@
       <c r="E1163" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1163" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1163" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1163" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
         <v>5306</v>
       </c>
@@ -64012,8 +65546,17 @@
       <c r="E1164" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1164" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1164" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1164" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
         <v>5308</v>
       </c>
@@ -64029,8 +65572,17 @@
       <c r="E1165" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1165" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1165" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1165" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
         <v>5310</v>
       </c>
@@ -64046,8 +65598,17 @@
       <c r="E1166" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1166" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1166" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1166" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
         <v>5312</v>
       </c>
@@ -64063,8 +65624,17 @@
       <c r="E1167" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1167" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1167" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1167" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
         <v>5314</v>
       </c>
@@ -64080,8 +65650,17 @@
       <c r="E1168" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1168" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1168" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1168" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
         <v>5316</v>
       </c>
@@ -64097,8 +65676,17 @@
       <c r="E1169" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1169" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1169" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1169" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
         <v>5318</v>
       </c>
@@ -64114,8 +65702,17 @@
       <c r="E1170" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1170" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1170" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1170" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
         <v>5320</v>
       </c>
@@ -64131,8 +65728,17 @@
       <c r="E1171" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1171" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1171" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1171" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
         <v>5322</v>
       </c>
@@ -64148,8 +65754,17 @@
       <c r="E1172" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1172" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1172" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1172" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
         <v>5324</v>
       </c>
@@ -64165,8 +65780,17 @@
       <c r="E1173" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1173" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1173" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1173" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
         <v>5325</v>
       </c>
@@ -64182,8 +65806,17 @@
       <c r="E1174" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1174" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1174" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1174" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
         <v>5326</v>
       </c>
@@ -64199,8 +65832,17 @@
       <c r="E1175" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1175" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1175" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1175" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
         <v>5327</v>
       </c>
@@ -64216,8 +65858,17 @@
       <c r="E1176" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1176" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1176" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1176" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
         <v>5328</v>
       </c>
@@ -64233,8 +65884,17 @@
       <c r="E1177" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1177" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1177" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1177" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
         <v>5329</v>
       </c>
@@ -64250,8 +65910,17 @@
       <c r="E1178" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1178" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1178" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1178" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
         <v>5330</v>
       </c>
@@ -64267,8 +65936,17 @@
       <c r="E1179" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1179" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1179" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1179" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
         <v>5331</v>
       </c>
@@ -64284,8 +65962,17 @@
       <c r="E1180" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1180" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1180" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1180" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
         <v>5332</v>
       </c>
@@ -64301,8 +65988,17 @@
       <c r="E1181" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1181" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1181" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1181" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
         <v>5333</v>
       </c>
@@ -64318,8 +66014,17 @@
       <c r="E1182" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1182" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1182" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1182" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
         <v>5334</v>
       </c>
@@ -64335,8 +66040,17 @@
       <c r="E1183" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1183" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1183" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1183" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
         <v>5336</v>
       </c>
@@ -64352,8 +66066,17 @@
       <c r="E1184" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1184" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1184" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1184" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
         <v>5338</v>
       </c>
@@ -64369,8 +66092,17 @@
       <c r="E1185" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1185" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1185" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1185" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
         <v>5340</v>
       </c>
@@ -64386,8 +66118,17 @@
       <c r="E1186" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1186" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1186" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1186" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
         <v>5342</v>
       </c>
@@ -64403,8 +66144,17 @@
       <c r="E1187" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1187" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1187" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1187" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
         <v>5344</v>
       </c>
@@ -64420,8 +66170,17 @@
       <c r="E1188" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1188" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1188" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1188" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
         <v>5346</v>
       </c>
@@ -64437,8 +66196,17 @@
       <c r="E1189" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1189" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1189" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1189" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
         <v>5348</v>
       </c>
@@ -64454,8 +66222,17 @@
       <c r="E1190" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1190" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1190" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1190" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
         <v>5350</v>
       </c>
@@ -64471,8 +66248,17 @@
       <c r="E1191" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1191" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1191" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1191" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
         <v>5352</v>
       </c>
@@ -64488,8 +66274,17 @@
       <c r="E1192" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1192" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1192" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
         <v>5354</v>
       </c>
@@ -64505,8 +66300,17 @@
       <c r="E1193" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1193" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1193" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
         <v>5356</v>
       </c>
@@ -64522,8 +66326,17 @@
       <c r="E1194" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1194" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1194" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
         <v>5358</v>
       </c>
@@ -64539,8 +66352,17 @@
       <c r="E1195" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1195" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1195" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
         <v>5360</v>
       </c>
@@ -64556,8 +66378,17 @@
       <c r="E1196" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1196" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1196" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
         <v>5362</v>
       </c>
@@ -64573,8 +66404,17 @@
       <c r="E1197" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1197" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1197" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
         <v>5364</v>
       </c>
@@ -64590,8 +66430,17 @@
       <c r="E1198" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1198" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1198" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
         <v>5366</v>
       </c>
@@ -64607,8 +66456,17 @@
       <c r="E1199" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1199" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1199" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
         <v>5368</v>
       </c>
@@ -64624,8 +66482,17 @@
       <c r="E1200" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1200" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1200" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
         <v>5370</v>
       </c>
@@ -64641,8 +66508,17 @@
       <c r="E1201" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1201" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1201" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
         <v>5372</v>
       </c>
@@ -64658,8 +66534,17 @@
       <c r="E1202" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1202" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1202" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
         <v>5374</v>
       </c>
@@ -64675,8 +66560,17 @@
       <c r="E1203" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1203" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1203" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
         <v>5376</v>
       </c>
@@ -64692,8 +66586,17 @@
       <c r="E1204" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1204" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1204" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
         <v>5378</v>
       </c>
@@ -64709,8 +66612,17 @@
       <c r="E1205" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1205" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1205" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
         <v>5380</v>
       </c>
@@ -64726,8 +66638,17 @@
       <c r="E1206" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1206" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1206" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1207" t="s">
         <v>5381</v>
       </c>
@@ -64743,8 +66664,17 @@
       <c r="E1207" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1207" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1207" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
         <v>5383</v>
       </c>
@@ -64760,8 +66690,17 @@
       <c r="E1208" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1208" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1208" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
         <v>5384</v>
       </c>
@@ -64777,8 +66716,17 @@
       <c r="E1209" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1209" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1209" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1210" t="s">
         <v>5386</v>
       </c>
@@ -64794,8 +66742,17 @@
       <c r="E1210" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1210" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1210" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1211" t="s">
         <v>5388</v>
       </c>
@@ -64811,8 +66768,17 @@
       <c r="E1211" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1211" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1211" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1212" t="s">
         <v>5390</v>
       </c>
@@ -64828,8 +66794,17 @@
       <c r="E1212" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1212" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1212" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
         <v>5392</v>
       </c>
@@ -64845,8 +66820,17 @@
       <c r="E1213" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1213" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1213" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
         <v>5393</v>
       </c>
@@ -64862,8 +66846,17 @@
       <c r="E1214" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1214" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1214" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
         <v>5395</v>
       </c>
@@ -64879,8 +66872,17 @@
       <c r="E1215" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1215" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1215" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
         <v>5396</v>
       </c>
@@ -64896,8 +66898,17 @@
       <c r="E1216" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1216" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1216" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
         <v>5398</v>
       </c>
@@ -64913,8 +66924,17 @@
       <c r="E1217" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1217" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1217" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
         <v>5399</v>
       </c>
@@ -64930,8 +66950,17 @@
       <c r="E1218" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1218" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1218" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
         <v>5400</v>
       </c>
@@ -64947,8 +66976,17 @@
       <c r="E1219" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1219" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1219" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
         <v>5401</v>
       </c>
@@ -64964,8 +67002,17 @@
       <c r="E1220" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1220" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1220" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
         <v>5403</v>
       </c>
@@ -64981,8 +67028,17 @@
       <c r="E1221" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1221" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1221" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
         <v>5404</v>
       </c>
@@ -64998,8 +67054,17 @@
       <c r="E1222" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1222" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1222" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
         <v>5406</v>
       </c>
@@ -65015,8 +67080,17 @@
       <c r="E1223" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1223" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1223" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
         <v>5407</v>
       </c>
@@ -65032,8 +67106,17 @@
       <c r="E1224" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1224" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1224" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
         <v>5408</v>
       </c>
@@ -65049,8 +67132,17 @@
       <c r="E1225" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1225" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1225" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
         <v>5409</v>
       </c>
@@ -65066,8 +67158,17 @@
       <c r="E1226" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1226" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1226" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
         <v>5410</v>
       </c>
@@ -65083,8 +67184,17 @@
       <c r="E1227" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1227" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1227" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
         <v>5411</v>
       </c>
@@ -65100,8 +67210,17 @@
       <c r="E1228" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1228" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1228" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
         <v>5413</v>
       </c>
@@ -65117,8 +67236,17 @@
       <c r="E1229" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1229" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1229" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
         <v>5415</v>
       </c>
@@ -65134,8 +67262,17 @@
       <c r="E1230" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1230" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1230" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
         <v>5417</v>
       </c>
@@ -65151,8 +67288,17 @@
       <c r="E1231" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1231" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1231" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
         <v>5419</v>
       </c>
@@ -65168,8 +67314,17 @@
       <c r="E1232" t="s">
         <v>5048</v>
       </c>
-    </row>
-    <row r="1233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H1232" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1232" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
         <v>5421</v>
       </c>
@@ -65184,6 +67339,15 @@
       </c>
       <c r="E1233" t="s">
         <v>5048</v>
+      </c>
+      <c r="H1233" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q1233" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
